--- a/df_final_NEW.xlsx
+++ b/df_final_NEW.xlsx
@@ -54292,7 +54292,7 @@
       </c>
       <c r="J962" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K962" t="inlineStr">
@@ -54348,7 +54348,7 @@
       </c>
       <c r="J963" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K963" t="inlineStr">
@@ -54404,7 +54404,7 @@
       </c>
       <c r="J964" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K964" t="inlineStr">
@@ -54460,7 +54460,7 @@
       </c>
       <c r="J965" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K965" t="inlineStr">
@@ -54516,7 +54516,7 @@
       </c>
       <c r="J966" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K966" t="inlineStr">
@@ -54572,7 +54572,7 @@
       </c>
       <c r="J967" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K967" t="inlineStr">
@@ -54628,7 +54628,7 @@
       </c>
       <c r="J968" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K968" t="inlineStr">
@@ -54684,7 +54684,7 @@
       </c>
       <c r="J969" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K969" t="inlineStr">
@@ -54740,7 +54740,7 @@
       </c>
       <c r="J970" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K970" t="inlineStr">
@@ -54796,7 +54796,7 @@
       </c>
       <c r="J971" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K971" t="inlineStr">
@@ -54852,7 +54852,7 @@
       </c>
       <c r="J972" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K972" t="inlineStr">
@@ -54908,7 +54908,7 @@
       </c>
       <c r="J973" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K973" t="inlineStr">
@@ -54964,7 +54964,7 @@
       </c>
       <c r="J974" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K974" t="inlineStr">
@@ -55020,7 +55020,7 @@
       </c>
       <c r="J975" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K975" t="inlineStr">
@@ -55076,7 +55076,7 @@
       </c>
       <c r="J976" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K976" t="inlineStr">
@@ -55132,7 +55132,7 @@
       </c>
       <c r="J977" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K977" t="inlineStr">
@@ -55188,7 +55188,7 @@
       </c>
       <c r="J978" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K978" t="inlineStr">
@@ -55244,7 +55244,7 @@
       </c>
       <c r="J979" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K979" t="inlineStr">
@@ -55300,7 +55300,7 @@
       </c>
       <c r="J980" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K980" t="inlineStr">
@@ -55356,7 +55356,7 @@
       </c>
       <c r="J981" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K981" t="inlineStr">
@@ -55412,7 +55412,7 @@
       </c>
       <c r="J982" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K982" t="inlineStr">
@@ -55468,7 +55468,7 @@
       </c>
       <c r="J983" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K983" t="inlineStr">
@@ -55524,7 +55524,7 @@
       </c>
       <c r="J984" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K984" t="inlineStr">
@@ -55580,7 +55580,7 @@
       </c>
       <c r="J985" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K985" t="inlineStr">
@@ -55636,7 +55636,7 @@
       </c>
       <c r="J986" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K986" t="inlineStr">
@@ -55692,7 +55692,7 @@
       </c>
       <c r="J987" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K987" t="inlineStr">
@@ -55748,7 +55748,7 @@
       </c>
       <c r="J988" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K988" t="inlineStr">
@@ -55804,7 +55804,7 @@
       </c>
       <c r="J989" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K989" t="inlineStr">
@@ -55860,7 +55860,7 @@
       </c>
       <c r="J990" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K990" t="inlineStr">
@@ -55916,7 +55916,7 @@
       </c>
       <c r="J991" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K991" t="inlineStr">
@@ -55972,7 +55972,7 @@
       </c>
       <c r="J992" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K992" t="inlineStr">
@@ -56028,7 +56028,7 @@
       </c>
       <c r="J993" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K993" t="inlineStr">
@@ -56084,7 +56084,7 @@
       </c>
       <c r="J994" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K994" t="inlineStr">
@@ -56140,7 +56140,7 @@
       </c>
       <c r="J995" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K995" t="inlineStr">
@@ -56196,7 +56196,7 @@
       </c>
       <c r="J996" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K996" t="inlineStr">
@@ -56252,7 +56252,7 @@
       </c>
       <c r="J997" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K997" t="inlineStr">
@@ -56308,7 +56308,7 @@
       </c>
       <c r="J998" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K998" t="inlineStr">
@@ -56364,7 +56364,7 @@
       </c>
       <c r="J999" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K999" t="inlineStr">
@@ -56420,7 +56420,7 @@
       </c>
       <c r="J1000" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1000" t="inlineStr">
@@ -56476,7 +56476,7 @@
       </c>
       <c r="J1001" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1001" t="inlineStr">
@@ -56532,7 +56532,7 @@
       </c>
       <c r="J1002" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1002" t="inlineStr">
@@ -56588,7 +56588,7 @@
       </c>
       <c r="J1003" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1003" t="inlineStr">
@@ -56644,7 +56644,7 @@
       </c>
       <c r="J1004" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1004" t="inlineStr">
@@ -56700,7 +56700,7 @@
       </c>
       <c r="J1005" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1005" t="inlineStr">
@@ -56756,7 +56756,7 @@
       </c>
       <c r="J1006" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1006" t="inlineStr">
@@ -56812,7 +56812,7 @@
       </c>
       <c r="J1007" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1007" t="inlineStr">
@@ -56868,7 +56868,7 @@
       </c>
       <c r="J1008" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1008" t="inlineStr">
@@ -56924,7 +56924,7 @@
       </c>
       <c r="J1009" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1009" t="inlineStr">
@@ -56980,7 +56980,7 @@
       </c>
       <c r="J1010" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1010" t="inlineStr">
@@ -57036,7 +57036,7 @@
       </c>
       <c r="J1011" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1011" t="inlineStr">
@@ -57092,7 +57092,7 @@
       </c>
       <c r="J1012" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1012" t="inlineStr">
@@ -57148,7 +57148,7 @@
       </c>
       <c r="J1013" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1013" t="inlineStr">
@@ -57204,7 +57204,7 @@
       </c>
       <c r="J1014" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1014" t="inlineStr">
@@ -57260,7 +57260,7 @@
       </c>
       <c r="J1015" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1015" t="inlineStr">
@@ -57316,7 +57316,7 @@
       </c>
       <c r="J1016" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1016" t="inlineStr">
@@ -57372,7 +57372,7 @@
       </c>
       <c r="J1017" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1017" t="inlineStr">
@@ -57428,7 +57428,7 @@
       </c>
       <c r="J1018" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1018" t="inlineStr">
@@ -57484,7 +57484,7 @@
       </c>
       <c r="J1019" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1019" t="inlineStr">
@@ -57540,7 +57540,7 @@
       </c>
       <c r="J1020" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1020" t="inlineStr">
@@ -57596,7 +57596,7 @@
       </c>
       <c r="J1021" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1021" t="inlineStr">
@@ -57652,7 +57652,7 @@
       </c>
       <c r="J1022" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1022" t="inlineStr">
@@ -57708,7 +57708,7 @@
       </c>
       <c r="J1023" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1023" t="inlineStr">
@@ -57764,7 +57764,7 @@
       </c>
       <c r="J1024" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1024" t="inlineStr">
@@ -57820,7 +57820,7 @@
       </c>
       <c r="J1025" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1025" t="inlineStr">
@@ -57876,7 +57876,7 @@
       </c>
       <c r="J1026" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1026" t="inlineStr">
@@ -57932,7 +57932,7 @@
       </c>
       <c r="J1027" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1027" t="inlineStr">
@@ -57988,7 +57988,7 @@
       </c>
       <c r="J1028" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1028" t="inlineStr">
@@ -58044,7 +58044,7 @@
       </c>
       <c r="J1029" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1029" t="inlineStr">
@@ -58100,7 +58100,7 @@
       </c>
       <c r="J1030" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1030" t="inlineStr">
@@ -58156,7 +58156,7 @@
       </c>
       <c r="J1031" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1031" t="inlineStr">
@@ -58212,7 +58212,7 @@
       </c>
       <c r="J1032" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1032" t="inlineStr">
@@ -58268,7 +58268,7 @@
       </c>
       <c r="J1033" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1033" t="inlineStr">
@@ -58324,7 +58324,7 @@
       </c>
       <c r="J1034" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1034" t="inlineStr">
@@ -58380,7 +58380,7 @@
       </c>
       <c r="J1035" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1035" t="inlineStr">
@@ -58436,7 +58436,7 @@
       </c>
       <c r="J1036" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1036" t="inlineStr">
@@ -58492,7 +58492,7 @@
       </c>
       <c r="J1037" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1037" t="inlineStr">
@@ -58548,7 +58548,7 @@
       </c>
       <c r="J1038" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1038" t="inlineStr">
@@ -58604,7 +58604,7 @@
       </c>
       <c r="J1039" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1039" t="inlineStr">
@@ -58660,7 +58660,7 @@
       </c>
       <c r="J1040" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1040" t="inlineStr">
@@ -58716,7 +58716,7 @@
       </c>
       <c r="J1041" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1041" t="inlineStr">
@@ -58772,7 +58772,7 @@
       </c>
       <c r="J1042" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1042" t="inlineStr">
@@ -58828,7 +58828,7 @@
       </c>
       <c r="J1043" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1043" t="inlineStr">
@@ -58884,7 +58884,7 @@
       </c>
       <c r="J1044" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1044" t="inlineStr">
@@ -58940,7 +58940,7 @@
       </c>
       <c r="J1045" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1045" t="inlineStr">
@@ -58996,7 +58996,7 @@
       </c>
       <c r="J1046" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1046" t="inlineStr">
@@ -59052,7 +59052,7 @@
       </c>
       <c r="J1047" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1047" t="inlineStr">
@@ -59108,7 +59108,7 @@
       </c>
       <c r="J1048" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1048" t="inlineStr">
@@ -59164,7 +59164,7 @@
       </c>
       <c r="J1049" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1049" t="inlineStr">
@@ -59220,7 +59220,7 @@
       </c>
       <c r="J1050" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1050" t="inlineStr">
@@ -59276,7 +59276,7 @@
       </c>
       <c r="J1051" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1051" t="inlineStr">
@@ -59332,7 +59332,7 @@
       </c>
       <c r="J1052" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1052" t="inlineStr">
@@ -59388,7 +59388,7 @@
       </c>
       <c r="J1053" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1053" t="inlineStr">
@@ -59444,7 +59444,7 @@
       </c>
       <c r="J1054" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1054" t="inlineStr">
@@ -59500,7 +59500,7 @@
       </c>
       <c r="J1055" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1055" t="inlineStr">
@@ -59556,7 +59556,7 @@
       </c>
       <c r="J1056" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1056" t="inlineStr">
@@ -59612,7 +59612,7 @@
       </c>
       <c r="J1057" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1057" t="inlineStr">
@@ -59668,7 +59668,7 @@
       </c>
       <c r="J1058" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1058" t="inlineStr">
@@ -59724,7 +59724,7 @@
       </c>
       <c r="J1059" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1059" t="inlineStr">
@@ -59780,7 +59780,7 @@
       </c>
       <c r="J1060" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1060" t="inlineStr">
@@ -59836,7 +59836,7 @@
       </c>
       <c r="J1061" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1061" t="inlineStr">
@@ -59892,7 +59892,7 @@
       </c>
       <c r="J1062" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1062" t="inlineStr">
@@ -59948,7 +59948,7 @@
       </c>
       <c r="J1063" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1063" t="inlineStr">
@@ -60004,7 +60004,7 @@
       </c>
       <c r="J1064" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1064" t="inlineStr">
@@ -60060,7 +60060,7 @@
       </c>
       <c r="J1065" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1065" t="inlineStr">
@@ -60116,7 +60116,7 @@
       </c>
       <c r="J1066" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1066" t="inlineStr">
@@ -60172,7 +60172,7 @@
       </c>
       <c r="J1067" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1067" t="inlineStr">
@@ -60228,7 +60228,7 @@
       </c>
       <c r="J1068" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1068" t="inlineStr">
@@ -60284,7 +60284,7 @@
       </c>
       <c r="J1069" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1069" t="inlineStr">
@@ -60340,7 +60340,7 @@
       </c>
       <c r="J1070" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1070" t="inlineStr">
@@ -60396,7 +60396,7 @@
       </c>
       <c r="J1071" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1071" t="inlineStr">
@@ -60452,7 +60452,7 @@
       </c>
       <c r="J1072" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1072" t="inlineStr">
@@ -60508,7 +60508,7 @@
       </c>
       <c r="J1073" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1073" t="inlineStr">
@@ -60564,7 +60564,7 @@
       </c>
       <c r="J1074" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1074" t="inlineStr">
@@ -60620,7 +60620,7 @@
       </c>
       <c r="J1075" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1075" t="inlineStr">
@@ -60676,7 +60676,7 @@
       </c>
       <c r="J1076" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1076" t="inlineStr">
@@ -60732,7 +60732,7 @@
       </c>
       <c r="J1077" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1077" t="inlineStr">
@@ -60788,7 +60788,7 @@
       </c>
       <c r="J1078" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1078" t="inlineStr">
@@ -60844,7 +60844,7 @@
       </c>
       <c r="J1079" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1079" t="inlineStr">
@@ -60900,7 +60900,7 @@
       </c>
       <c r="J1080" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1080" t="inlineStr">
@@ -60956,7 +60956,7 @@
       </c>
       <c r="J1081" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1081" t="inlineStr">
@@ -61012,7 +61012,7 @@
       </c>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1082" t="inlineStr">
@@ -61068,7 +61068,7 @@
       </c>
       <c r="J1083" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1083" t="inlineStr">
@@ -61124,7 +61124,7 @@
       </c>
       <c r="J1084" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1084" t="inlineStr">
@@ -61180,7 +61180,7 @@
       </c>
       <c r="J1085" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1085" t="inlineStr">
@@ -61236,7 +61236,7 @@
       </c>
       <c r="J1086" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1086" t="inlineStr">
@@ -61292,7 +61292,7 @@
       </c>
       <c r="J1087" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1087" t="inlineStr">
@@ -61348,7 +61348,7 @@
       </c>
       <c r="J1088" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1088" t="inlineStr">
@@ -61404,7 +61404,7 @@
       </c>
       <c r="J1089" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1089" t="inlineStr">
@@ -61460,7 +61460,7 @@
       </c>
       <c r="J1090" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1090" t="inlineStr">
@@ -61516,7 +61516,7 @@
       </c>
       <c r="J1091" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1091" t="inlineStr">
@@ -61572,7 +61572,7 @@
       </c>
       <c r="J1092" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1092" t="inlineStr">
@@ -61628,7 +61628,7 @@
       </c>
       <c r="J1093" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1093" t="inlineStr">
@@ -61684,7 +61684,7 @@
       </c>
       <c r="J1094" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1094" t="inlineStr">
@@ -61740,7 +61740,7 @@
       </c>
       <c r="J1095" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1095" t="inlineStr">
@@ -61796,7 +61796,7 @@
       </c>
       <c r="J1096" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1096" t="inlineStr">
@@ -61852,7 +61852,7 @@
       </c>
       <c r="J1097" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1097" t="inlineStr">
@@ -61908,7 +61908,7 @@
       </c>
       <c r="J1098" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1098" t="inlineStr">
@@ -61964,7 +61964,7 @@
       </c>
       <c r="J1099" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1099" t="inlineStr">
@@ -62020,7 +62020,7 @@
       </c>
       <c r="J1100" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1100" t="inlineStr">
@@ -62076,7 +62076,7 @@
       </c>
       <c r="J1101" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1101" t="inlineStr">
@@ -62132,7 +62132,7 @@
       </c>
       <c r="J1102" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1102" t="inlineStr">
@@ -62188,7 +62188,7 @@
       </c>
       <c r="J1103" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1103" t="inlineStr">
@@ -62244,7 +62244,7 @@
       </c>
       <c r="J1104" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1104" t="inlineStr">
@@ -62300,7 +62300,7 @@
       </c>
       <c r="J1105" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1105" t="inlineStr">
@@ -62356,7 +62356,7 @@
       </c>
       <c r="J1106" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1106" t="inlineStr">
@@ -62412,7 +62412,7 @@
       </c>
       <c r="J1107" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1107" t="inlineStr">
@@ -62468,7 +62468,7 @@
       </c>
       <c r="J1108" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1108" t="inlineStr">
@@ -62524,7 +62524,7 @@
       </c>
       <c r="J1109" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1109" t="inlineStr">
@@ -62580,7 +62580,7 @@
       </c>
       <c r="J1110" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1110" t="inlineStr">
@@ -62636,7 +62636,7 @@
       </c>
       <c r="J1111" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1111" t="inlineStr">
@@ -62692,7 +62692,7 @@
       </c>
       <c r="J1112" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1112" t="inlineStr">
@@ -62748,7 +62748,7 @@
       </c>
       <c r="J1113" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1113" t="inlineStr">
@@ -62804,7 +62804,7 @@
       </c>
       <c r="J1114" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1114" t="inlineStr">
@@ -62860,7 +62860,7 @@
       </c>
       <c r="J1115" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1115" t="inlineStr">
@@ -62916,7 +62916,7 @@
       </c>
       <c r="J1116" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1116" t="inlineStr">
@@ -62972,7 +62972,7 @@
       </c>
       <c r="J1117" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1117" t="inlineStr">
@@ -63028,7 +63028,7 @@
       </c>
       <c r="J1118" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1118" t="inlineStr">
@@ -63084,7 +63084,7 @@
       </c>
       <c r="J1119" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1119" t="inlineStr">
@@ -63140,7 +63140,7 @@
       </c>
       <c r="J1120" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1120" t="inlineStr">
@@ -63196,7 +63196,7 @@
       </c>
       <c r="J1121" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1121" t="inlineStr">
@@ -63252,7 +63252,7 @@
       </c>
       <c r="J1122" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1122" t="inlineStr">
@@ -63308,7 +63308,7 @@
       </c>
       <c r="J1123" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1123" t="inlineStr">
@@ -63364,7 +63364,7 @@
       </c>
       <c r="J1124" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1124" t="inlineStr">
@@ -63420,7 +63420,7 @@
       </c>
       <c r="J1125" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1125" t="inlineStr">
@@ -63476,7 +63476,7 @@
       </c>
       <c r="J1126" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1126" t="inlineStr">
@@ -63532,7 +63532,7 @@
       </c>
       <c r="J1127" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1127" t="inlineStr">
@@ -63588,7 +63588,7 @@
       </c>
       <c r="J1128" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1128" t="inlineStr">
@@ -63644,7 +63644,7 @@
       </c>
       <c r="J1129" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1129" t="inlineStr">
@@ -63700,7 +63700,7 @@
       </c>
       <c r="J1130" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1130" t="inlineStr">
@@ -63756,7 +63756,7 @@
       </c>
       <c r="J1131" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1131" t="inlineStr">
@@ -63812,7 +63812,7 @@
       </c>
       <c r="J1132" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1132" t="inlineStr">
@@ -63868,7 +63868,7 @@
       </c>
       <c r="J1133" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1133" t="inlineStr">
@@ -63924,7 +63924,7 @@
       </c>
       <c r="J1134" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1134" t="inlineStr">
@@ -63980,7 +63980,7 @@
       </c>
       <c r="J1135" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1135" t="inlineStr">
@@ -64036,7 +64036,7 @@
       </c>
       <c r="J1136" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1136" t="inlineStr">
@@ -64092,7 +64092,7 @@
       </c>
       <c r="J1137" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1137" t="inlineStr">
@@ -64148,7 +64148,7 @@
       </c>
       <c r="J1138" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1138" t="inlineStr">
@@ -64204,7 +64204,7 @@
       </c>
       <c r="J1139" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1139" t="inlineStr">
@@ -64260,7 +64260,7 @@
       </c>
       <c r="J1140" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1140" t="inlineStr">
@@ -64316,7 +64316,7 @@
       </c>
       <c r="J1141" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1141" t="inlineStr">
@@ -64372,7 +64372,7 @@
       </c>
       <c r="J1142" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1142" t="inlineStr">
@@ -64428,7 +64428,7 @@
       </c>
       <c r="J1143" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1143" t="inlineStr">
@@ -64484,7 +64484,7 @@
       </c>
       <c r="J1144" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1144" t="inlineStr">
@@ -64540,7 +64540,7 @@
       </c>
       <c r="J1145" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1145" t="inlineStr">
@@ -64596,7 +64596,7 @@
       </c>
       <c r="J1146" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1146" t="inlineStr">
@@ -64652,7 +64652,7 @@
       </c>
       <c r="J1147" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1147" t="inlineStr">
@@ -64708,7 +64708,7 @@
       </c>
       <c r="J1148" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1148" t="inlineStr">
@@ -64764,7 +64764,7 @@
       </c>
       <c r="J1149" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1149" t="inlineStr">
@@ -64820,7 +64820,7 @@
       </c>
       <c r="J1150" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1150" t="inlineStr">
@@ -64876,7 +64876,7 @@
       </c>
       <c r="J1151" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1151" t="inlineStr">
@@ -64932,7 +64932,7 @@
       </c>
       <c r="J1152" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1152" t="inlineStr">
@@ -64988,7 +64988,7 @@
       </c>
       <c r="J1153" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1153" t="inlineStr">
@@ -65044,7 +65044,7 @@
       </c>
       <c r="J1154" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1154" t="inlineStr">
@@ -65100,7 +65100,7 @@
       </c>
       <c r="J1155" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1155" t="inlineStr">
@@ -65156,7 +65156,7 @@
       </c>
       <c r="J1156" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1156" t="inlineStr">
@@ -65212,7 +65212,7 @@
       </c>
       <c r="J1157" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1157" t="inlineStr">
@@ -65268,7 +65268,7 @@
       </c>
       <c r="J1158" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1158" t="inlineStr">
@@ -65324,7 +65324,7 @@
       </c>
       <c r="J1159" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1159" t="inlineStr">
@@ -65380,7 +65380,7 @@
       </c>
       <c r="J1160" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1160" t="inlineStr">
@@ -65436,7 +65436,7 @@
       </c>
       <c r="J1161" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1161" t="inlineStr">
@@ -65492,7 +65492,7 @@
       </c>
       <c r="J1162" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1162" t="inlineStr">
@@ -65548,7 +65548,7 @@
       </c>
       <c r="J1163" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1163" t="inlineStr">
@@ -65604,7 +65604,7 @@
       </c>
       <c r="J1164" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1164" t="inlineStr">
@@ -65660,7 +65660,7 @@
       </c>
       <c r="J1165" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1165" t="inlineStr">
@@ -65716,7 +65716,7 @@
       </c>
       <c r="J1166" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1166" t="inlineStr">
@@ -65772,7 +65772,7 @@
       </c>
       <c r="J1167" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1167" t="inlineStr">
@@ -65828,7 +65828,7 @@
       </c>
       <c r="J1168" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1168" t="inlineStr">
@@ -65884,7 +65884,7 @@
       </c>
       <c r="J1169" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1169" t="inlineStr">
@@ -65940,7 +65940,7 @@
       </c>
       <c r="J1170" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1170" t="inlineStr">
@@ -65996,7 +65996,7 @@
       </c>
       <c r="J1171" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1171" t="inlineStr">
@@ -66052,7 +66052,7 @@
       </c>
       <c r="J1172" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1172" t="inlineStr">
@@ -66108,7 +66108,7 @@
       </c>
       <c r="J1173" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1173" t="inlineStr">
@@ -66164,7 +66164,7 @@
       </c>
       <c r="J1174" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1174" t="inlineStr">
@@ -66220,7 +66220,7 @@
       </c>
       <c r="J1175" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1175" t="inlineStr">
@@ -66276,7 +66276,7 @@
       </c>
       <c r="J1176" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1176" t="inlineStr">
@@ -66332,7 +66332,7 @@
       </c>
       <c r="J1177" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1177" t="inlineStr">
@@ -66388,7 +66388,7 @@
       </c>
       <c r="J1178" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1178" t="inlineStr">
@@ -66444,7 +66444,7 @@
       </c>
       <c r="J1179" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1179" t="inlineStr">
@@ -66500,7 +66500,7 @@
       </c>
       <c r="J1180" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1180" t="inlineStr">
@@ -66556,7 +66556,7 @@
       </c>
       <c r="J1181" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1181" t="inlineStr">
@@ -66612,7 +66612,7 @@
       </c>
       <c r="J1182" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1182" t="inlineStr">
@@ -66668,7 +66668,7 @@
       </c>
       <c r="J1183" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1183" t="inlineStr">
@@ -66724,7 +66724,7 @@
       </c>
       <c r="J1184" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1184" t="inlineStr">
@@ -66780,7 +66780,7 @@
       </c>
       <c r="J1185" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1185" t="inlineStr">
@@ -66836,7 +66836,7 @@
       </c>
       <c r="J1186" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1186" t="inlineStr">
@@ -66892,7 +66892,7 @@
       </c>
       <c r="J1187" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1187" t="inlineStr">
@@ -66948,7 +66948,7 @@
       </c>
       <c r="J1188" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1188" t="inlineStr">
@@ -67004,7 +67004,7 @@
       </c>
       <c r="J1189" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1189" t="inlineStr">
@@ -67060,7 +67060,7 @@
       </c>
       <c r="J1190" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1190" t="inlineStr">
@@ -67116,7 +67116,7 @@
       </c>
       <c r="J1191" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1191" t="inlineStr">
@@ -67172,7 +67172,7 @@
       </c>
       <c r="J1192" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1192" t="inlineStr">
@@ -67228,7 +67228,7 @@
       </c>
       <c r="J1193" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1193" t="inlineStr">
@@ -67284,7 +67284,7 @@
       </c>
       <c r="J1194" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1194" t="inlineStr">
@@ -67340,7 +67340,7 @@
       </c>
       <c r="J1195" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1195" t="inlineStr">
@@ -67396,7 +67396,7 @@
       </c>
       <c r="J1196" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1196" t="inlineStr">
@@ -67452,7 +67452,7 @@
       </c>
       <c r="J1197" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1197" t="inlineStr">
@@ -67508,7 +67508,7 @@
       </c>
       <c r="J1198" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1198" t="inlineStr">
@@ -67564,7 +67564,7 @@
       </c>
       <c r="J1199" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1199" t="inlineStr">
@@ -67620,7 +67620,7 @@
       </c>
       <c r="J1200" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1200" t="inlineStr">
@@ -67676,7 +67676,7 @@
       </c>
       <c r="J1201" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1201" t="inlineStr">
@@ -67732,7 +67732,7 @@
       </c>
       <c r="J1202" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1202" t="inlineStr">
@@ -67788,7 +67788,7 @@
       </c>
       <c r="J1203" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1203" t="inlineStr">
@@ -67844,7 +67844,7 @@
       </c>
       <c r="J1204" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1204" t="inlineStr">
@@ -67900,7 +67900,7 @@
       </c>
       <c r="J1205" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1205" t="inlineStr">
@@ -67956,7 +67956,7 @@
       </c>
       <c r="J1206" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1206" t="inlineStr">
@@ -68012,7 +68012,7 @@
       </c>
       <c r="J1207" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1207" t="inlineStr">
@@ -68068,7 +68068,7 @@
       </c>
       <c r="J1208" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1208" t="inlineStr">
@@ -68124,7 +68124,7 @@
       </c>
       <c r="J1209" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1209" t="inlineStr">
@@ -68180,7 +68180,7 @@
       </c>
       <c r="J1210" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1210" t="inlineStr">
@@ -68236,7 +68236,7 @@
       </c>
       <c r="J1211" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1211" t="inlineStr">
@@ -68292,7 +68292,7 @@
       </c>
       <c r="J1212" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1212" t="inlineStr">
@@ -68348,7 +68348,7 @@
       </c>
       <c r="J1213" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1213" t="inlineStr">
@@ -68404,7 +68404,7 @@
       </c>
       <c r="J1214" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1214" t="inlineStr">
@@ -68460,7 +68460,7 @@
       </c>
       <c r="J1215" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1215" t="inlineStr">
@@ -68516,7 +68516,7 @@
       </c>
       <c r="J1216" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1216" t="inlineStr">
@@ -68572,7 +68572,7 @@
       </c>
       <c r="J1217" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1217" t="inlineStr">
@@ -68628,7 +68628,7 @@
       </c>
       <c r="J1218" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1218" t="inlineStr">
@@ -68684,7 +68684,7 @@
       </c>
       <c r="J1219" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1219" t="inlineStr">
@@ -68740,7 +68740,7 @@
       </c>
       <c r="J1220" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1220" t="inlineStr">
@@ -68796,7 +68796,7 @@
       </c>
       <c r="J1221" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1221" t="inlineStr">
@@ -68852,7 +68852,7 @@
       </c>
       <c r="J1222" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1222" t="inlineStr">
@@ -68908,7 +68908,7 @@
       </c>
       <c r="J1223" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1223" t="inlineStr">
@@ -68964,7 +68964,7 @@
       </c>
       <c r="J1224" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1224" t="inlineStr">
@@ -69020,7 +69020,7 @@
       </c>
       <c r="J1225" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1225" t="inlineStr">
@@ -69076,7 +69076,7 @@
       </c>
       <c r="J1226" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1226" t="inlineStr">
@@ -69132,7 +69132,7 @@
       </c>
       <c r="J1227" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1227" t="inlineStr">
@@ -69188,7 +69188,7 @@
       </c>
       <c r="J1228" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1228" t="inlineStr">
@@ -69244,7 +69244,7 @@
       </c>
       <c r="J1229" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1229" t="inlineStr">
@@ -69300,7 +69300,7 @@
       </c>
       <c r="J1230" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1230" t="inlineStr">
@@ -69356,7 +69356,7 @@
       </c>
       <c r="J1231" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1231" t="inlineStr">
@@ -69412,7 +69412,7 @@
       </c>
       <c r="J1232" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1232" t="inlineStr">
@@ -69468,7 +69468,7 @@
       </c>
       <c r="J1233" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1233" t="inlineStr">
@@ -69524,7 +69524,7 @@
       </c>
       <c r="J1234" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1234" t="inlineStr">
@@ -69580,7 +69580,7 @@
       </c>
       <c r="J1235" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1235" t="inlineStr">
@@ -69636,7 +69636,7 @@
       </c>
       <c r="J1236" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1236" t="inlineStr">
@@ -69692,7 +69692,7 @@
       </c>
       <c r="J1237" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1237" t="inlineStr">
@@ -69748,7 +69748,7 @@
       </c>
       <c r="J1238" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1238" t="inlineStr">
@@ -69804,7 +69804,7 @@
       </c>
       <c r="J1239" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1239" t="inlineStr">
@@ -69860,7 +69860,7 @@
       </c>
       <c r="J1240" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1240" t="inlineStr">
@@ -69916,7 +69916,7 @@
       </c>
       <c r="J1241" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1241" t="inlineStr">
@@ -69972,7 +69972,7 @@
       </c>
       <c r="J1242" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1242" t="inlineStr">
@@ -70028,7 +70028,7 @@
       </c>
       <c r="J1243" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1243" t="inlineStr">
@@ -70084,7 +70084,7 @@
       </c>
       <c r="J1244" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1244" t="inlineStr">
@@ -70140,7 +70140,7 @@
       </c>
       <c r="J1245" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1245" t="inlineStr">
@@ -70196,7 +70196,7 @@
       </c>
       <c r="J1246" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1246" t="inlineStr">
@@ -70252,7 +70252,7 @@
       </c>
       <c r="J1247" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1247" t="inlineStr">
@@ -70308,7 +70308,7 @@
       </c>
       <c r="J1248" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1248" t="inlineStr">
@@ -70364,7 +70364,7 @@
       </c>
       <c r="J1249" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1249" t="inlineStr">
@@ -70420,7 +70420,7 @@
       </c>
       <c r="J1250" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1250" t="inlineStr">
@@ -70476,7 +70476,7 @@
       </c>
       <c r="J1251" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1251" t="inlineStr">
@@ -70532,7 +70532,7 @@
       </c>
       <c r="J1252" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1252" t="inlineStr">
@@ -70588,7 +70588,7 @@
       </c>
       <c r="J1253" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1253" t="inlineStr">
@@ -70644,7 +70644,7 @@
       </c>
       <c r="J1254" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1254" t="inlineStr">
@@ -70700,7 +70700,7 @@
       </c>
       <c r="J1255" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1255" t="inlineStr">
@@ -70756,7 +70756,7 @@
       </c>
       <c r="J1256" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1256" t="inlineStr">
@@ -70812,7 +70812,7 @@
       </c>
       <c r="J1257" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1257" t="inlineStr">
@@ -70868,7 +70868,7 @@
       </c>
       <c r="J1258" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1258" t="inlineStr">
@@ -70924,7 +70924,7 @@
       </c>
       <c r="J1259" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1259" t="inlineStr">
@@ -70980,7 +70980,7 @@
       </c>
       <c r="J1260" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1260" t="inlineStr">
@@ -71036,7 +71036,7 @@
       </c>
       <c r="J1261" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1261" t="inlineStr">
@@ -71092,7 +71092,7 @@
       </c>
       <c r="J1262" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1262" t="inlineStr">
@@ -71148,7 +71148,7 @@
       </c>
       <c r="J1263" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1263" t="inlineStr">
@@ -71204,7 +71204,7 @@
       </c>
       <c r="J1264" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1264" t="inlineStr">
@@ -71260,7 +71260,7 @@
       </c>
       <c r="J1265" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1265" t="inlineStr">
@@ -71316,7 +71316,7 @@
       </c>
       <c r="J1266" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1266" t="inlineStr">
@@ -71372,7 +71372,7 @@
       </c>
       <c r="J1267" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1267" t="inlineStr">
@@ -71428,7 +71428,7 @@
       </c>
       <c r="J1268" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1268" t="inlineStr">
@@ -71484,7 +71484,7 @@
       </c>
       <c r="J1269" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1269" t="inlineStr">
@@ -71540,7 +71540,7 @@
       </c>
       <c r="J1270" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1270" t="inlineStr">
@@ -71596,7 +71596,7 @@
       </c>
       <c r="J1271" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1271" t="inlineStr">
@@ -71652,7 +71652,7 @@
       </c>
       <c r="J1272" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1272" t="inlineStr">
@@ -71708,7 +71708,7 @@
       </c>
       <c r="J1273" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1273" t="inlineStr">
@@ -71764,7 +71764,7 @@
       </c>
       <c r="J1274" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1274" t="inlineStr">
@@ -71820,7 +71820,7 @@
       </c>
       <c r="J1275" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1275" t="inlineStr">
@@ -71876,7 +71876,7 @@
       </c>
       <c r="J1276" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1276" t="inlineStr">
@@ -71932,7 +71932,7 @@
       </c>
       <c r="J1277" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1277" t="inlineStr">
@@ -71988,7 +71988,7 @@
       </c>
       <c r="J1278" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1278" t="inlineStr">
@@ -72044,7 +72044,7 @@
       </c>
       <c r="J1279" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1279" t="inlineStr">
@@ -72100,7 +72100,7 @@
       </c>
       <c r="J1280" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1280" t="inlineStr">
@@ -72156,7 +72156,7 @@
       </c>
       <c r="J1281" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1281" t="inlineStr">
@@ -72212,7 +72212,7 @@
       </c>
       <c r="J1282" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1282" t="inlineStr">
@@ -72268,7 +72268,7 @@
       </c>
       <c r="J1283" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1283" t="inlineStr">
@@ -72324,7 +72324,7 @@
       </c>
       <c r="J1284" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1284" t="inlineStr">
@@ -72380,7 +72380,7 @@
       </c>
       <c r="J1285" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1285" t="inlineStr">
@@ -72436,7 +72436,7 @@
       </c>
       <c r="J1286" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1286" t="inlineStr">
@@ -72492,7 +72492,7 @@
       </c>
       <c r="J1287" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1287" t="inlineStr">
@@ -72548,7 +72548,7 @@
       </c>
       <c r="J1288" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1288" t="inlineStr">
@@ -72604,7 +72604,7 @@
       </c>
       <c r="J1289" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1289" t="inlineStr">
@@ -72660,7 +72660,7 @@
       </c>
       <c r="J1290" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1290" t="inlineStr">
@@ -72716,7 +72716,7 @@
       </c>
       <c r="J1291" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1291" t="inlineStr">
@@ -72772,7 +72772,7 @@
       </c>
       <c r="J1292" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1292" t="inlineStr">
@@ -72828,7 +72828,7 @@
       </c>
       <c r="J1293" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1293" t="inlineStr">
@@ -72884,7 +72884,7 @@
       </c>
       <c r="J1294" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1294" t="inlineStr">
@@ -72940,7 +72940,7 @@
       </c>
       <c r="J1295" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1295" t="inlineStr">
@@ -72996,7 +72996,7 @@
       </c>
       <c r="J1296" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1296" t="inlineStr">
@@ -73052,7 +73052,7 @@
       </c>
       <c r="J1297" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1297" t="inlineStr">
@@ -73108,7 +73108,7 @@
       </c>
       <c r="J1298" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1298" t="inlineStr">
@@ -73164,7 +73164,7 @@
       </c>
       <c r="J1299" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1299" t="inlineStr">
@@ -73220,7 +73220,7 @@
       </c>
       <c r="J1300" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1300" t="inlineStr">
@@ -73276,7 +73276,7 @@
       </c>
       <c r="J1301" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1301" t="inlineStr">
@@ -73332,7 +73332,7 @@
       </c>
       <c r="J1302" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1302" t="inlineStr">
@@ -73388,7 +73388,7 @@
       </c>
       <c r="J1303" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1303" t="inlineStr">
@@ -73444,7 +73444,7 @@
       </c>
       <c r="J1304" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1304" t="inlineStr">
@@ -73500,7 +73500,7 @@
       </c>
       <c r="J1305" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1305" t="inlineStr">
@@ -73556,7 +73556,7 @@
       </c>
       <c r="J1306" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1306" t="inlineStr">
@@ -73612,7 +73612,7 @@
       </c>
       <c r="J1307" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1307" t="inlineStr">
@@ -73668,7 +73668,7 @@
       </c>
       <c r="J1308" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1308" t="inlineStr">
@@ -73724,7 +73724,7 @@
       </c>
       <c r="J1309" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1309" t="inlineStr">
@@ -73780,7 +73780,7 @@
       </c>
       <c r="J1310" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1310" t="inlineStr">
@@ -73836,7 +73836,7 @@
       </c>
       <c r="J1311" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1311" t="inlineStr">
@@ -73892,7 +73892,7 @@
       </c>
       <c r="J1312" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1312" t="inlineStr">
@@ -73948,7 +73948,7 @@
       </c>
       <c r="J1313" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1313" t="inlineStr">
@@ -74004,7 +74004,7 @@
       </c>
       <c r="J1314" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1314" t="inlineStr">
@@ -74060,7 +74060,7 @@
       </c>
       <c r="J1315" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1315" t="inlineStr">
@@ -74116,7 +74116,7 @@
       </c>
       <c r="J1316" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1316" t="inlineStr">
@@ -74172,7 +74172,7 @@
       </c>
       <c r="J1317" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1317" t="inlineStr">
@@ -74228,7 +74228,7 @@
       </c>
       <c r="J1318" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1318" t="inlineStr">
@@ -74284,7 +74284,7 @@
       </c>
       <c r="J1319" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1319" t="inlineStr">
@@ -74340,7 +74340,7 @@
       </c>
       <c r="J1320" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1320" t="inlineStr">
@@ -74396,7 +74396,7 @@
       </c>
       <c r="J1321" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1321" t="inlineStr">
@@ -74452,7 +74452,7 @@
       </c>
       <c r="J1322" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1322" t="inlineStr">
@@ -74508,7 +74508,7 @@
       </c>
       <c r="J1323" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1323" t="inlineStr">
@@ -74564,7 +74564,7 @@
       </c>
       <c r="J1324" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1324" t="inlineStr">
@@ -74620,7 +74620,7 @@
       </c>
       <c r="J1325" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1325" t="inlineStr">
@@ -74676,7 +74676,7 @@
       </c>
       <c r="J1326" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1326" t="inlineStr">
@@ -74732,7 +74732,7 @@
       </c>
       <c r="J1327" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1327" t="inlineStr">
@@ -74788,7 +74788,7 @@
       </c>
       <c r="J1328" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1328" t="inlineStr">
@@ -74844,7 +74844,7 @@
       </c>
       <c r="J1329" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1329" t="inlineStr">
@@ -74900,7 +74900,7 @@
       </c>
       <c r="J1330" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1330" t="inlineStr">
@@ -74956,7 +74956,7 @@
       </c>
       <c r="J1331" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1331" t="inlineStr">
@@ -75012,7 +75012,7 @@
       </c>
       <c r="J1332" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1332" t="inlineStr">
@@ -75068,7 +75068,7 @@
       </c>
       <c r="J1333" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1333" t="inlineStr">
@@ -75124,7 +75124,7 @@
       </c>
       <c r="J1334" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1334" t="inlineStr">
@@ -75180,7 +75180,7 @@
       </c>
       <c r="J1335" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1335" t="inlineStr">
@@ -75236,7 +75236,7 @@
       </c>
       <c r="J1336" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1336" t="inlineStr">
@@ -75292,7 +75292,7 @@
       </c>
       <c r="J1337" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1337" t="inlineStr">
@@ -75348,7 +75348,7 @@
       </c>
       <c r="J1338" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1338" t="inlineStr">
@@ -75404,7 +75404,7 @@
       </c>
       <c r="J1339" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1339" t="inlineStr">
@@ -75460,7 +75460,7 @@
       </c>
       <c r="J1340" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1340" t="inlineStr">
@@ -75516,7 +75516,7 @@
       </c>
       <c r="J1341" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1341" t="inlineStr">
@@ -75572,7 +75572,7 @@
       </c>
       <c r="J1342" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1342" t="inlineStr">
@@ -75628,7 +75628,7 @@
       </c>
       <c r="J1343" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1343" t="inlineStr">
@@ -75684,7 +75684,7 @@
       </c>
       <c r="J1344" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1344" t="inlineStr">
@@ -75740,7 +75740,7 @@
       </c>
       <c r="J1345" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1345" t="inlineStr">
@@ -75796,7 +75796,7 @@
       </c>
       <c r="J1346" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1346" t="inlineStr">
@@ -75852,7 +75852,7 @@
       </c>
       <c r="J1347" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1347" t="inlineStr">
@@ -75908,7 +75908,7 @@
       </c>
       <c r="J1348" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1348" t="inlineStr">
@@ -75964,7 +75964,7 @@
       </c>
       <c r="J1349" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1349" t="inlineStr">
@@ -76020,7 +76020,7 @@
       </c>
       <c r="J1350" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1350" t="inlineStr">
@@ -76076,7 +76076,7 @@
       </c>
       <c r="J1351" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1351" t="inlineStr">
@@ -76132,7 +76132,7 @@
       </c>
       <c r="J1352" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1352" t="inlineStr">
@@ -76188,7 +76188,7 @@
       </c>
       <c r="J1353" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1353" t="inlineStr">
@@ -76244,7 +76244,7 @@
       </c>
       <c r="J1354" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1354" t="inlineStr">
@@ -76300,7 +76300,7 @@
       </c>
       <c r="J1355" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1355" t="inlineStr">
@@ -76356,7 +76356,7 @@
       </c>
       <c r="J1356" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1356" t="inlineStr">
@@ -76412,7 +76412,7 @@
       </c>
       <c r="J1357" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1357" t="inlineStr">
@@ -76468,7 +76468,7 @@
       </c>
       <c r="J1358" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1358" t="inlineStr">
@@ -76524,7 +76524,7 @@
       </c>
       <c r="J1359" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1359" t="inlineStr">
@@ -76580,7 +76580,7 @@
       </c>
       <c r="J1360" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1360" t="inlineStr">
@@ -76636,7 +76636,7 @@
       </c>
       <c r="J1361" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1361" t="inlineStr">
@@ -76692,7 +76692,7 @@
       </c>
       <c r="J1362" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1362" t="inlineStr">
@@ -76748,7 +76748,7 @@
       </c>
       <c r="J1363" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1363" t="inlineStr">
@@ -76804,7 +76804,7 @@
       </c>
       <c r="J1364" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1364" t="inlineStr">
@@ -76860,7 +76860,7 @@
       </c>
       <c r="J1365" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1365" t="inlineStr">
@@ -76916,7 +76916,7 @@
       </c>
       <c r="J1366" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1366" t="inlineStr">
@@ -76972,7 +76972,7 @@
       </c>
       <c r="J1367" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1367" t="inlineStr">
@@ -77028,7 +77028,7 @@
       </c>
       <c r="J1368" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1368" t="inlineStr">
@@ -77084,7 +77084,7 @@
       </c>
       <c r="J1369" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1369" t="inlineStr">
@@ -77140,7 +77140,7 @@
       </c>
       <c r="J1370" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1370" t="inlineStr">
@@ -77196,7 +77196,7 @@
       </c>
       <c r="J1371" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1371" t="inlineStr">
@@ -77252,7 +77252,7 @@
       </c>
       <c r="J1372" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1372" t="inlineStr">
@@ -77308,7 +77308,7 @@
       </c>
       <c r="J1373" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1373" t="inlineStr">
@@ -77364,7 +77364,7 @@
       </c>
       <c r="J1374" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1374" t="inlineStr">
@@ -77420,7 +77420,7 @@
       </c>
       <c r="J1375" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1375" t="inlineStr">
@@ -77476,7 +77476,7 @@
       </c>
       <c r="J1376" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1376" t="inlineStr">
@@ -77532,7 +77532,7 @@
       </c>
       <c r="J1377" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1377" t="inlineStr">
@@ -77588,7 +77588,7 @@
       </c>
       <c r="J1378" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1378" t="inlineStr">
@@ -77644,7 +77644,7 @@
       </c>
       <c r="J1379" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1379" t="inlineStr">
@@ -77700,7 +77700,7 @@
       </c>
       <c r="J1380" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1380" t="inlineStr">
@@ -77756,7 +77756,7 @@
       </c>
       <c r="J1381" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1381" t="inlineStr">
@@ -77812,7 +77812,7 @@
       </c>
       <c r="J1382" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1382" t="inlineStr">
@@ -77868,7 +77868,7 @@
       </c>
       <c r="J1383" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1383" t="inlineStr">
@@ -77924,7 +77924,7 @@
       </c>
       <c r="J1384" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1384" t="inlineStr">
@@ -77980,7 +77980,7 @@
       </c>
       <c r="J1385" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1385" t="inlineStr">
@@ -78036,7 +78036,7 @@
       </c>
       <c r="J1386" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1386" t="inlineStr">
@@ -78092,7 +78092,7 @@
       </c>
       <c r="J1387" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1387" t="inlineStr">
@@ -78148,7 +78148,7 @@
       </c>
       <c r="J1388" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1388" t="inlineStr">
@@ -78204,7 +78204,7 @@
       </c>
       <c r="J1389" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1389" t="inlineStr">
@@ -78260,7 +78260,7 @@
       </c>
       <c r="J1390" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1390" t="inlineStr">
@@ -78316,7 +78316,7 @@
       </c>
       <c r="J1391" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1391" t="inlineStr">
@@ -78372,7 +78372,7 @@
       </c>
       <c r="J1392" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1392" t="inlineStr">
@@ -78428,7 +78428,7 @@
       </c>
       <c r="J1393" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1393" t="inlineStr">
@@ -78484,7 +78484,7 @@
       </c>
       <c r="J1394" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1394" t="inlineStr">
@@ -78540,7 +78540,7 @@
       </c>
       <c r="J1395" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1395" t="inlineStr">
@@ -78596,7 +78596,7 @@
       </c>
       <c r="J1396" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1396" t="inlineStr">
@@ -78652,7 +78652,7 @@
       </c>
       <c r="J1397" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1397" t="inlineStr">
@@ -78708,7 +78708,7 @@
       </c>
       <c r="J1398" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1398" t="inlineStr">
@@ -78764,7 +78764,7 @@
       </c>
       <c r="J1399" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1399" t="inlineStr">
@@ -78820,7 +78820,7 @@
       </c>
       <c r="J1400" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1400" t="inlineStr">
@@ -78876,7 +78876,7 @@
       </c>
       <c r="J1401" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1401" t="inlineStr">
@@ -78932,7 +78932,7 @@
       </c>
       <c r="J1402" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1402" t="inlineStr">
@@ -78988,7 +78988,7 @@
       </c>
       <c r="J1403" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1403" t="inlineStr">
@@ -79044,7 +79044,7 @@
       </c>
       <c r="J1404" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1404" t="inlineStr">
@@ -79100,7 +79100,7 @@
       </c>
       <c r="J1405" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1405" t="inlineStr">
@@ -79156,7 +79156,7 @@
       </c>
       <c r="J1406" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1406" t="inlineStr">
@@ -79212,7 +79212,7 @@
       </c>
       <c r="J1407" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1407" t="inlineStr">
@@ -79268,7 +79268,7 @@
       </c>
       <c r="J1408" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1408" t="inlineStr">
@@ -79324,7 +79324,7 @@
       </c>
       <c r="J1409" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1409" t="inlineStr">
@@ -79380,7 +79380,7 @@
       </c>
       <c r="J1410" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1410" t="inlineStr">
@@ -79436,7 +79436,7 @@
       </c>
       <c r="J1411" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1411" t="inlineStr">
@@ -79492,7 +79492,7 @@
       </c>
       <c r="J1412" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1412" t="inlineStr">
@@ -79548,7 +79548,7 @@
       </c>
       <c r="J1413" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1413" t="inlineStr">
@@ -79604,7 +79604,7 @@
       </c>
       <c r="J1414" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1414" t="inlineStr">
@@ -79660,7 +79660,7 @@
       </c>
       <c r="J1415" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1415" t="inlineStr">
@@ -79716,7 +79716,7 @@
       </c>
       <c r="J1416" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1416" t="inlineStr">
@@ -79772,7 +79772,7 @@
       </c>
       <c r="J1417" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1417" t="inlineStr">
@@ -79828,7 +79828,7 @@
       </c>
       <c r="J1418" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1418" t="inlineStr">
@@ -79884,7 +79884,7 @@
       </c>
       <c r="J1419" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1419" t="inlineStr">
@@ -79940,7 +79940,7 @@
       </c>
       <c r="J1420" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1420" t="inlineStr">
@@ -79996,7 +79996,7 @@
       </c>
       <c r="J1421" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1421" t="inlineStr">
@@ -80052,7 +80052,7 @@
       </c>
       <c r="J1422" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1422" t="inlineStr">
@@ -80108,7 +80108,7 @@
       </c>
       <c r="J1423" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1423" t="inlineStr">
@@ -80164,7 +80164,7 @@
       </c>
       <c r="J1424" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1424" t="inlineStr">
@@ -80220,7 +80220,7 @@
       </c>
       <c r="J1425" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1425" t="inlineStr">
@@ -80276,7 +80276,7 @@
       </c>
       <c r="J1426" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1426" t="inlineStr">
@@ -80332,7 +80332,7 @@
       </c>
       <c r="J1427" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1427" t="inlineStr">
@@ -80388,7 +80388,7 @@
       </c>
       <c r="J1428" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1428" t="inlineStr">
@@ -80444,7 +80444,7 @@
       </c>
       <c r="J1429" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1429" t="inlineStr">
@@ -80500,7 +80500,7 @@
       </c>
       <c r="J1430" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1430" t="inlineStr">
@@ -80556,7 +80556,7 @@
       </c>
       <c r="J1431" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1431" t="inlineStr">
@@ -80612,7 +80612,7 @@
       </c>
       <c r="J1432" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1432" t="inlineStr">
@@ -80668,7 +80668,7 @@
       </c>
       <c r="J1433" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1433" t="inlineStr">
@@ -80724,7 +80724,7 @@
       </c>
       <c r="J1434" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1434" t="inlineStr">
@@ -80780,7 +80780,7 @@
       </c>
       <c r="J1435" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1435" t="inlineStr">
@@ -80836,7 +80836,7 @@
       </c>
       <c r="J1436" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1436" t="inlineStr">
@@ -80892,7 +80892,7 @@
       </c>
       <c r="J1437" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Posgrado</t>
         </is>
       </c>
       <c r="K1437" t="inlineStr">
@@ -80948,7 +80948,7 @@
       </c>
       <c r="J1438" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1438" t="inlineStr">
@@ -81004,7 +81004,7 @@
       </c>
       <c r="J1439" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1439" t="inlineStr">
@@ -81060,7 +81060,7 @@
       </c>
       <c r="J1440" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1440" t="inlineStr">
@@ -81116,7 +81116,7 @@
       </c>
       <c r="J1441" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1441" t="inlineStr">
@@ -81172,7 +81172,7 @@
       </c>
       <c r="J1442" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1442" t="inlineStr">
@@ -81228,7 +81228,7 @@
       </c>
       <c r="J1443" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1443" t="inlineStr">
@@ -81284,7 +81284,7 @@
       </c>
       <c r="J1444" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1444" t="inlineStr">
@@ -81340,7 +81340,7 @@
       </c>
       <c r="J1445" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1445" t="inlineStr">
@@ -81396,7 +81396,7 @@
       </c>
       <c r="J1446" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1446" t="inlineStr">
@@ -81452,7 +81452,7 @@
       </c>
       <c r="J1447" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1447" t="inlineStr">
@@ -81508,7 +81508,7 @@
       </c>
       <c r="J1448" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1448" t="inlineStr">
@@ -81564,7 +81564,7 @@
       </c>
       <c r="J1449" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1449" t="inlineStr">
@@ -81620,7 +81620,7 @@
       </c>
       <c r="J1450" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1450" t="inlineStr">
@@ -81676,7 +81676,7 @@
       </c>
       <c r="J1451" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1451" t="inlineStr">
@@ -81732,7 +81732,7 @@
       </c>
       <c r="J1452" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1452" t="inlineStr">
@@ -81788,7 +81788,7 @@
       </c>
       <c r="J1453" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Pregrado</t>
         </is>
       </c>
       <c r="K1453" t="inlineStr">
